--- a/data_folder/bev_electronics_all_measured/input_data/case.xlsx
+++ b/data_folder/bev_electronics_all_measured/input_data/case.xlsx
@@ -572,12 +572,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -684,7 +684,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_not_dismantled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -711,32 +711,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F_loss_dismantling</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>element</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>recovered</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -768,29 +768,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>recovered</t>
+          <t>loss</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pyro</t>
+          <t>hammer_mill</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>recovered</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -832,39 +832,39 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>recovered</t>
+          <t>loss</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>F_not_dismantled</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>F_shredded</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>hulk_transfer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>component</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>intermediate</t>
         </is>
       </c>
     </row>
@@ -890,19 +890,19 @@
   <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,7 @@
           <t>0.95</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1080,6 +1081,7 @@
           <t>0.5</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1142,6 +1144,7 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1204,6 +1207,7 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1238,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_not_dismantled</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1253,15 +1257,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.34</v>
-      </c>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1274,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER. Was a derived residual; given an asymmetric band reaching 25% of the way to each bound so this case has no residual rows. Carries no measurement.</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE: fraction of Motors left in the car; the two ranges it merges, added</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1305,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_not_dismantled</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1311,15 +1320,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.4875</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.7375</v>
-      </c>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.5075</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.8375</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>dismantling</t>
@@ -1332,131 +1346,133 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER. Was a derived residual; given an asymmetric band reaching 25% of the way to each bound so this case has no residual rows. Carries no measurement.</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE: fraction of Wiring left in the car; the two ranges it merges, added</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>F_loss_dismantling</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>element</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motors</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: losses during dismantling</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium oxidises to slag in a pyro route</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>F_dismantled</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>F_loss_dismantling</t>
+          <t>F_refined</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>element</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wiring</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>refining</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>pyro</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: losses during dismantling</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: reports to the copper matte</t>
         </is>
       </c>
     </row>
@@ -1488,24 +1504,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.3</t>
-        </is>
-      </c>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1518,7 +1535,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium oxidises to slag in a pyro route</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: winding copper, bound up with steel and magnets</t>
         </is>
       </c>
     </row>
@@ -1550,24 +1567,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.95</t>
-        </is>
-      </c>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1580,7 +1598,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: reports to the copper matte</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -1612,24 +1630,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.96</t>
-        </is>
-      </c>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1642,7 +1661,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: winding copper, bound up with steel and magnets</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1693,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1689,9 +1708,10 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.6</t>
-        </is>
-      </c>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1704,7 +1724,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1756,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1751,9 +1771,10 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1766,7 +1787,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: copper smelter sends rare earths to slag; dedicated magnet recovery does not. The range spans both</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1819,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1813,9 +1834,10 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1828,7 +1850,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal, incidental recovery</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1882,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1878,6 +1900,7 @@
           <t>0.6</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1890,7 +1913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: copper smelter sends rare earths to slag; dedicated magnet recovery does not. The range spans both</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1945,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1937,9 +1960,10 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.6</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>refining</t>
@@ -1952,7 +1976,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1993,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1984,24 +2008,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.6</t>
-        </is>
-      </c>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2014,7 +2039,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: clean harness copper into a copper smelter</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2061,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2046,24 +2071,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>0.925</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2076,7 +2102,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER. Was a derived residual; given an asymmetric band reaching 25% of the way to each bound so this case has no residual rows. Carries no measurement.</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2119,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wiring_mixed</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>F_refined</t>
+          <t>F_loss_refining</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2108,24 +2134,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.1125</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.98</t>
-        </is>
-      </c>
+          <t>0.3625</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2138,7 +2165,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: clean harness copper into a copper smelter</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER. Was a derived residual; given an asymmetric band reaching 25% of the way to each bound so this case has no residual rows. Carries no measurement.</t>
         </is>
       </c>
     </row>
@@ -2170,20 +2197,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.925</v>
-      </c>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.325</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2228,20 +2260,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1125</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.3625</v>
-      </c>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2286,20 +2323,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.325</v>
-      </c>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.7125</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.9625</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2344,20 +2386,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.925</v>
-      </c>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.7125</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.9625</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2402,20 +2449,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>0.7125</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.9625</v>
-      </c>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2460,20 +2512,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>0.7125</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.9625</v>
-      </c>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2518,7 +2575,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2526,12 +2583,17 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.925</v>
-      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.925</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2576,20 +2638,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.925</v>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2602,7 +2669,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER. Was a derived residual; given an asymmetric band reaching 25% of the way to each bound so this case has no residual rows. Carries no measurement.</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2686,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2634,20 +2701,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.925</v>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.0375</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.2875</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>refining</t>
@@ -2667,7 +2739,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2682,7 +2754,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2692,44 +2764,45 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>pyro</t>
+          <t>hammer_mill</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium separates reasonably well</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2739,12 +2812,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wiring_mixed</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>F_loss_refining</t>
+          <t>F_recovered_shredder</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2754,33 +2827,38 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.2875</v>
-      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>refining</t>
+          <t>shredding</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>pyro</t>
+          <t>hammer_mill</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER. Was a derived residual; given an asymmetric band reaching 25% of the way to each bound so this case has no residual rows. Carries no measurement.</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: largely follows the ferrous fraction</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2890,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2830,6 +2908,7 @@
           <t>0.7</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -2842,7 +2921,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: aluminium separates reasonably well</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: more of it trapped with the ferrous fraction</t>
         </is>
       </c>
     </row>
@@ -2874,24 +2953,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -2904,7 +2984,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: largely follows the ferrous fraction</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -2936,24 +3016,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.7</t>
-        </is>
-      </c>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -2966,7 +3047,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: more of it trapped with the ferrous fraction</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
         </is>
       </c>
     </row>
@@ -2998,12 +3079,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3013,9 +3094,10 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3028,7 +3110,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3142,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3075,9 +3157,10 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3090,7 +3173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: a shredded magnet disperses and is lost</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3205,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3137,9 +3220,10 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3152,7 +3236,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: trace metal in a shredded stream</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3268,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3202,6 +3286,7 @@
           <t>0.05</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3214,7 +3299,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: a shredded magnet disperses and is lost</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3331,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3261,9 +3346,10 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3276,7 +3362,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3379,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3308,24 +3394,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3338,7 +3425,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: follows Nd</t>
+          <t>PLACEHOLDER (Claude, not data) -- replace: harness copper partly recovered from the non-ferrous fraction, partly lost to shredder residue</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3447,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3370,24 +3457,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3400,7 +3488,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER. Was a derived residual; given an asymmetric band reaching 25% of the way to each bound so this case has no residual rows. Carries no measurement.</t>
         </is>
       </c>
     </row>
@@ -3417,12 +3505,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wiring_mixed</t>
+          <t>Motors_mixed</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>F_recovered_shredder</t>
+          <t>F_loss_shredding</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3432,24 +3520,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.6375</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.75</t>
-        </is>
-      </c>
+          <t>0.8875</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3462,7 +3551,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- replace: harness copper partly recovered from the non-ferrous fraction, partly lost to shredder residue</t>
+          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER. Was a derived residual; given an asymmetric band reaching 25% of the way to each bound so this case has no residual rows. Carries no measurement.</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3583,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3502,12 +3591,17 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.625</v>
-      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3552,20 +3646,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Dy</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>0.6375</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.8875</v>
-      </c>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3610,20 +3709,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Ga</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.625</v>
-      </c>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.985</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3668,20 +3772,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dy</t>
+          <t>Nb</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>0.7425</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.9925</v>
-      </c>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.985</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3726,20 +3835,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ga</t>
+          <t>Nd</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.985</v>
-      </c>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3784,20 +3898,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nb</t>
+          <t>Pr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.985</v>
-      </c>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3842,7 +3961,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nd</t>
+          <t>Tb</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3850,12 +3969,17 @@
           <t>0.99</t>
         </is>
       </c>
-      <c r="H49" t="n">
-        <v>0.7425</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.9925</v>
-      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.7425</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.9925</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3900,20 +4024,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pr</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>0.7425</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.9925</v>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3926,7 +4055,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER. Was a derived residual; given an asymmetric band reaching 25% of the way to each bound so this case has no residual rows. Carries no measurement.</t>
+          <t>decision: unspecified material is not recovered</t>
         </is>
       </c>
     </row>
@@ -3943,7 +4072,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Motors_mixed</t>
+          <t>Wiring_mixed</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3958,20 +4087,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tb</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>0.7425</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.9925</v>
-      </c>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.3375</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.5875</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>shredding</t>
@@ -3991,32 +4125,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>F_not_dismantled</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>F_shredded</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Motors_mixed</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>component</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>Motors</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4024,114 +4158,81 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>hulk_transfer</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>definitional: a hulk that was not dismantled goes to the shredder. Not measured -- there is nowhere else for it to go.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>F_not_dismantled</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>F_shredded</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Wiring_mixed</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>component</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Wiring</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.5875</v>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>hulk_transfer</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- REPLACE WITH YOUR NUMBER. Was a derived residual; given an asymmetric band reaching 25% of the way to each bound so this case has no residual rows. Carries no measurement.</t>
+          <t>definitional: a hulk that was not dismantled goes to the shredder. Not measured -- there is nowhere else for it to go.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation sqref="A2:A53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$A$2:$A$10</formula1>
-    </dataValidation>
-    <dataValidation sqref="B2:B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$B$2:$B$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$C$2:$C$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$D$2:$D$10</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$E$2:$E$13</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$F$2:$F$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$G$2:$G$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
